--- a/SERVICE/ExcelCauHinh/Settup AXE.xlsx
+++ b/SERVICE/ExcelCauHinh/Settup AXE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\ToolAXE\CauHinhHeThongAXE\IIS\ExcelCauHinh\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\ToolAXE\CauHinhHeThongAXE\SERVICE\ExcelCauHinh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B33C765-5D55-4437-8890-99157C97562F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6E54E88-08DE-48D5-915C-C200C2CFC66C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cài đặt IIS" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="103">
   <si>
     <t>Thông tin chung</t>
   </si>
@@ -210,60 +210,18 @@
     <t>Path ldf</t>
   </si>
   <si>
-    <t>AXE_CORE_ACC.bak</t>
-  </si>
-  <si>
-    <t>AXE_CORE_ACC</t>
-  </si>
-  <si>
-    <t>AXE_CORE_CLOUD.bak</t>
-  </si>
-  <si>
-    <t>AXE_CORE_CLOUD</t>
-  </si>
-  <si>
-    <t>AXE_CORE_CNF.bak</t>
-  </si>
-  <si>
-    <t>AXE_CORE_LOG.bak</t>
-  </si>
-  <si>
-    <t>AXE_CORE_MSG.bak</t>
-  </si>
-  <si>
-    <t>AXE_CORE_STG.bak</t>
-  </si>
-  <si>
     <t>Tên Service OCR</t>
   </si>
   <si>
-    <t>ServiceAXALogic</t>
-  </si>
-  <si>
-    <t>sc create ServiceAXALogic binPath= "C:\Web\ServiceLogic\ServiceDocpro.exe" start= auto</t>
-  </si>
-  <si>
     <t>Đường dẫn gốc chứa app Service OCR</t>
   </si>
   <si>
-    <t>C:\Web\ServiceLogic\ServiceDocpro.exe</t>
-  </si>
-  <si>
     <t>Tên Service Export</t>
   </si>
   <si>
-    <t>ServiceAXASendmail</t>
-  </si>
-  <si>
-    <t>sc create ServiceAXASendmail binPath= "C:\Web\ServiceSendmail\DocProServiceSendMail.exe" start= auto</t>
-  </si>
-  <si>
     <t>Đường dẫn gốc chứa app Service Export</t>
   </si>
   <si>
-    <t>C:\Web\ServiceSendmail\DocProServiceSendMail.exe</t>
-  </si>
-  <si>
     <t>Script</t>
   </si>
   <si>
@@ -343,6 +301,42 @@
   </si>
   <si>
     <t>http://localhost:1221</t>
+  </si>
+  <si>
+    <t>AXE_CORE_2026_ACC.bak</t>
+  </si>
+  <si>
+    <t>AXE_CORE_2026_CLOUD.bak</t>
+  </si>
+  <si>
+    <t>AXE_CORE_2026_CNF.bak</t>
+  </si>
+  <si>
+    <t>AXE_CORE_2026_LOG.bak</t>
+  </si>
+  <si>
+    <t>AXE_CORE_2026_MSG.bak</t>
+  </si>
+  <si>
+    <t>AXE_CORE_2026_STG.bak</t>
+  </si>
+  <si>
+    <t>AXE_CORE_2026_ACC</t>
+  </si>
+  <si>
+    <t>AXE_CORE_2026_CLOUD</t>
+  </si>
+  <si>
+    <t>E:\TestTool_Dựng web\ServiceExport\DocProService.exe</t>
+  </si>
+  <si>
+    <t>E:\TestTool_Dựng web\ServiceOCR\DocProService.exe</t>
+  </si>
+  <si>
+    <t>AXEServiceExport_CuongTest</t>
+  </si>
+  <si>
+    <t>AXEServiceOCR_CuongTest</t>
   </si>
 </sst>
 </file>
@@ -631,50 +625,50 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -988,15 +982,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
       <c r="G1" s="12"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
@@ -1009,68 +1003,68 @@
         <v>3</v>
       </c>
       <c r="G2" s="12"/>
-      <c r="H2" s="46"/>
+      <c r="H2" s="40"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="C3" s="17"/>
       <c r="G3" s="12"/>
-      <c r="H3" s="47"/>
+      <c r="H3" s="41"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="12"/>
-      <c r="H4" s="47"/>
+      <c r="H4" s="41"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C5" s="17"/>
       <c r="G5" s="12"/>
-      <c r="H5" s="47"/>
+      <c r="H5" s="41"/>
     </row>
     <row r="6" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>9</v>
       </c>
       <c r="G6" s="12"/>
-      <c r="H6" s="47"/>
+      <c r="H6" s="41"/>
     </row>
     <row r="7" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>9</v>
       </c>
       <c r="G7" s="12"/>
-      <c r="H7" s="47"/>
+      <c r="H7" s="41"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
@@ -1081,17 +1075,17 @@
       </c>
       <c r="C8" s="17"/>
       <c r="G8" s="12"/>
-      <c r="H8" s="48"/>
+      <c r="H8" s="42"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
       <c r="G9" s="12"/>
       <c r="H9" s="20"/>
     </row>
@@ -1133,14 +1127,14 @@
       <c r="H12" s="21"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="39" t="s">
+      <c r="A13" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="41"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="50"/>
       <c r="G13" s="12"/>
       <c r="H13" s="13"/>
     </row>
@@ -1203,14 +1197,14 @@
       <c r="H16" s="21"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="39" t="s">
+      <c r="A17" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="40"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
+      <c r="B17" s="46"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
       <c r="G17" s="12"/>
       <c r="H17" s="13"/>
     </row>
@@ -1249,10 +1243,10 @@
       <c r="D19" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="36" t="s">
+      <c r="E19" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="F19" s="36"/>
+      <c r="F19" s="49"/>
       <c r="G19" s="12"/>
       <c r="H19" s="21" t="str">
         <f t="shared" ref="H19:H24" si="1">IF(D19="","",$B$8&amp;" add app  /site.name:"""&amp;B19&amp;""" /path:/"&amp;A19&amp;" /physicalPath:"&amp;C19&amp;"")</f>
@@ -1274,10 +1268,10 @@
       <c r="D20" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="36" t="s">
+      <c r="E20" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="36"/>
+      <c r="F20" s="49"/>
       <c r="G20" s="12"/>
       <c r="H20" s="21" t="str">
         <f t="shared" si="1"/>
@@ -1299,10 +1293,10 @@
       <c r="D21" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="36" t="s">
+      <c r="E21" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="F21" s="36"/>
+      <c r="F21" s="49"/>
       <c r="G21" s="12"/>
       <c r="H21" s="21" t="str">
         <f t="shared" si="1"/>
@@ -1324,10 +1318,10 @@
       <c r="D22" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="36" t="s">
+      <c r="E22" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="36"/>
+      <c r="F22" s="49"/>
       <c r="G22" s="12"/>
       <c r="H22" s="21" t="str">
         <f t="shared" si="1"/>
@@ -1349,10 +1343,10 @@
       <c r="D23" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="E23" s="36" t="s">
+      <c r="E23" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="36"/>
+      <c r="F23" s="49"/>
       <c r="G23" s="12"/>
       <c r="H23" s="21" t="str">
         <f t="shared" si="1"/>
@@ -1374,10 +1368,10 @@
       <c r="D24" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="E24" s="36" t="s">
+      <c r="E24" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="F24" s="36"/>
+      <c r="F24" s="49"/>
       <c r="G24" s="12"/>
       <c r="H24" s="21" t="str">
         <f t="shared" si="1"/>
@@ -1389,20 +1383,20 @@
       <c r="B25" s="21"/>
       <c r="C25" s="17"/>
       <c r="D25" s="21"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
       <c r="G25" s="12"/>
       <c r="H25" s="21"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="38"/>
-      <c r="C26" s="38"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
       <c r="H26" s="13"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1439,14 +1433,14 @@
       <c r="H29" s="21"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="45" t="s">
+      <c r="A30" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="45"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
       <c r="H30" s="21"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1459,11 +1453,11 @@
       <c r="C31" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="50" t="s">
+      <c r="D31" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="E31" s="50"/>
-      <c r="F31" s="50"/>
+      <c r="E31" s="44"/>
+      <c r="F31" s="44"/>
       <c r="H31" s="21"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1478,9 +1472,9 @@
         <f>$A$11</f>
         <v>AXE_Test-Web</v>
       </c>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="36"/>
+      <c r="D32" s="49"/>
+      <c r="E32" s="49"/>
+      <c r="F32" s="49"/>
       <c r="H32" s="21" t="str">
         <f>IF(C32="","",$B$8&amp;" set app "&amp;A32&amp;"/"&amp;B32&amp;"  /"&amp;"applicationPool:"&amp;C32&amp;"")</f>
         <v>c:\Windows\system32\inetsrv\appcmd set app AXE_Test_Web/login  /applicationPool:AXE_Test-Web</v>
@@ -1498,9 +1492,9 @@
         <f t="shared" ref="C33:C37" si="3">$A$11</f>
         <v>AXE_Test-Web</v>
       </c>
-      <c r="D33" s="49"/>
-      <c r="E33" s="49"/>
-      <c r="F33" s="49"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="43"/>
       <c r="H33" s="21" t="str">
         <f>IF(C33="","",$B$8&amp;" set app "&amp;A33&amp;"/"&amp;B33&amp;"  /"&amp;"applicationPool:"&amp;C33&amp;"")</f>
         <v>c:\Windows\system32\inetsrv\appcmd set app AXE_Test_Web/admin  /applicationPool:AXE_Test-Web</v>
@@ -1518,9 +1512,9 @@
         <f t="shared" si="3"/>
         <v>AXE_Test-Web</v>
       </c>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
       <c r="H34" s="21" t="str">
         <f>IF(C34="","",$B$8&amp;" set app "&amp;A34&amp;"/"&amp;B34&amp;"  /"&amp;"applicationPool:"&amp;C34&amp;"")</f>
         <v>c:\Windows\system32\inetsrv\appcmd set app AXE_Test_Web/resumable  /applicationPool:AXE_Test-Web</v>
@@ -1538,9 +1532,9 @@
         <f t="shared" si="3"/>
         <v>AXE_Test-Web</v>
       </c>
-      <c r="D35" s="49"/>
-      <c r="E35" s="49"/>
-      <c r="F35" s="49"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="43"/>
       <c r="H35" s="21" t="str">
         <f>IF(C35="","",$B$8&amp;" set app "&amp;A35&amp;"/"&amp;B35&amp;"  /"&amp;"applicationPool:"&amp;C35&amp;"")</f>
         <v>c:\Windows\system32\inetsrv\appcmd set app AXE_Test_Web/uploader  /applicationPool:AXE_Test-Web</v>
@@ -1558,9 +1552,9 @@
         <f t="shared" si="3"/>
         <v>AXE_Test-Web</v>
       </c>
-      <c r="D36" s="49"/>
-      <c r="E36" s="49"/>
-      <c r="F36" s="49"/>
+      <c r="D36" s="43"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="43"/>
       <c r="H36" s="21" t="str">
         <f>IF(C36="","","c:\Windows\system32\inetsrv\appcmd set app "&amp;A36&amp;"/"&amp;B36&amp;"  /"&amp;"applicationPool:"&amp;C36&amp;"")</f>
         <v>c:\Windows\system32\inetsrv\appcmd set app AXE_Test_Web/storage  /applicationPool:AXE_Test-Web</v>
@@ -1578,9 +1572,9 @@
         <f t="shared" si="3"/>
         <v>AXE_Test-Web</v>
       </c>
-      <c r="D37" s="42"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="44"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="37"/>
+      <c r="F37" s="38"/>
       <c r="H37" s="21" t="str">
         <f t="shared" ref="H37:H38" si="4">IF(C37="","","c:\Windows\system32\inetsrv\appcmd set app "&amp;A37&amp;"/"&amp;B37&amp;"  /"&amp;"applicationPool:"&amp;C37&amp;"")</f>
         <v>c:\Windows\system32\inetsrv\appcmd set app AXE_Test_Web/doc  /applicationPool:AXE_Test-Web</v>
@@ -1590,9 +1584,9 @@
       <c r="A38" s="21"/>
       <c r="B38" s="21"/>
       <c r="C38" s="17"/>
-      <c r="D38" s="42"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="44"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="37"/>
+      <c r="F38" s="38"/>
       <c r="H38" s="21" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -1600,6 +1594,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
     <mergeCell ref="D37:F37"/>
     <mergeCell ref="D38:F38"/>
     <mergeCell ref="H1:J1"/>
@@ -1616,13 +1617,6 @@
     <mergeCell ref="D35:F35"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E23:F23"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K427:K1048576 G26:G426 K1:K25 B18 G9:G10" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -1658,19 +1652,19 @@
     <col min="4" max="4" width="42.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="41.109375" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="255.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="255.44140625" style="11" customWidth="1"/>
+    <col min="8" max="8" width="10.109375" style="11" customWidth="1"/>
     <col min="9" max="9" width="36.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="8.88671875" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
       <c r="D1" s="26"/>
       <c r="E1" s="26"/>
       <c r="F1" s="12"/>
@@ -1689,7 +1683,7 @@
       <c r="D2" s="31"/>
       <c r="E2" s="31"/>
       <c r="F2" s="12"/>
-      <c r="G2" s="46"/>
+      <c r="G2" s="40"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
@@ -1700,7 +1694,7 @@
       </c>
       <c r="C3" s="21"/>
       <c r="F3" s="12"/>
-      <c r="G3" s="47"/>
+      <c r="G3" s="41"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
@@ -1711,7 +1705,7 @@
       </c>
       <c r="C4" s="21"/>
       <c r="F4" s="12"/>
-      <c r="G4" s="47"/>
+      <c r="G4" s="41"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
@@ -1722,7 +1716,7 @@
       </c>
       <c r="C5" s="21"/>
       <c r="F5" s="12"/>
-      <c r="G5" s="47"/>
+      <c r="G5" s="41"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
@@ -1733,14 +1727,14 @@
       </c>
       <c r="C6" s="21"/>
       <c r="F6" s="12"/>
-      <c r="G6" s="47"/>
+      <c r="G6" s="41"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
       <c r="D7" s="26"/>
       <c r="E7" s="26"/>
       <c r="F7" s="12"/>
@@ -1774,11 +1768,11 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="37" t="s">
+      <c r="A10" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
       <c r="D10" s="26"/>
       <c r="E10" s="26"/>
       <c r="F10" s="12"/>
@@ -1804,11 +1798,11 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="39" t="s">
+      <c r="A13" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
       <c r="D13" s="26"/>
       <c r="E13" s="26"/>
       <c r="F13" s="12"/>
@@ -1835,22 +1829,22 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="B15" s="27" t="str">
         <f>B3&amp;A15</f>
-        <v>E:\BACKUP\AXE_CORE_ACC.bak</v>
+        <v>E:\BACKUP\AXE_CORE_2026_ACC.bak</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D15" s="30" t="str">
         <f>$B$4&amp;$C15&amp;".mdf"</f>
-        <v>E:\DATABASE\AXE_CORE_ACC.mdf</v>
+        <v>E:\DATABASE\AXE_CORE_2026_ACC.mdf</v>
       </c>
       <c r="E15" s="30" t="str">
         <f>$B$4&amp;$C15&amp;".ldf"</f>
-        <v>E:\DATABASE\AXE_CORE_ACC.ldf</v>
+        <v>E:\DATABASE\AXE_CORE_2026_ACC.ldf</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="35" t="str">
@@ -1866,35 +1860,35 @@
 &amp;"EXEC "&amp;$C15&amp;".sys.sp_executesql N'CREATE USER "&amp;$B$5&amp;" FOR LOGIN "&amp;$B$5&amp;"';
 EXEC "&amp;$C15&amp;".sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER "&amp;$B$5&amp;"';"</f>
         <v>INSERT INTO #FileList (LogicalName, PhysicalName, Type, FileGroupName, Size, MaxSize, FileId, CreateLSN, DropLSN, UniqueId, ReadOnlyLSN, ReadWriteLSN, BackupSizeInBytes, SourceBlockSize, FileGroupId, LogGroupGUID, DifferentialBaseLSN, DifferentialBaseGUID, IsReadOnly, IsPresent, TDEThumbprint, SnapshotUrl)
-EXEC ('RESTORE FILELISTONLY FROM DISK = ''E:\BACKUP\AXE_CORE_ACC.bak''');
-UPDATE #FileList SET PhysicalPath = 'E:\BACKUP\AXE_CORE_ACC.bak' WHERE PhysicalPath IS NULL;
-set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_ACC.bak');
-set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_ACC.bak');
-RESTORE DATABASE AXE_CORE_ACC FROM DISK = 'E:\BACKUP\AXE_CORE_ACC.bak'
+EXEC ('RESTORE FILELISTONLY FROM DISK = ''E:\BACKUP\AXE_CORE_2026_ACC.bak''');
+UPDATE #FileList SET PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_ACC.bak' WHERE PhysicalPath IS NULL;
+set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_ACC.bak');
+set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_ACC.bak');
+RESTORE DATABASE AXE_CORE_2026_ACC FROM DISK = 'E:\BACKUP\AXE_CORE_2026_ACC.bak'
 WITH 
-MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_ACC.mdf',
-MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_ACC.ldf', REPLACE;EXEC AXE_CORE_ACC.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
-EXEC AXE_CORE_ACC.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
+MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_2026_ACC.mdf',
+MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_2026_ACC.ldf', REPLACE;EXEC AXE_CORE_2026_ACC.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
+EXEC AXE_CORE_2026_ACC.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="B16" s="30" t="str">
         <f>B3&amp;A16</f>
-        <v>E:\BACKUP\AXE_CORE_CLOUD.bak</v>
+        <v>E:\BACKUP\AXE_CORE_2026_CLOUD.bak</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D16" s="30" t="str">
         <f>$B$4&amp;$C16&amp;".mdf"</f>
-        <v>E:\DATABASE\AXE_CORE_CLOUD.mdf</v>
+        <v>E:\DATABASE\AXE_CORE_2026_CLOUD.mdf</v>
       </c>
       <c r="E16" s="30" t="str">
         <f>$B$4&amp;$C16&amp;".ldf"</f>
-        <v>E:\DATABASE\AXE_CORE_CLOUD.ldf</v>
+        <v>E:\DATABASE\AXE_CORE_2026_CLOUD.ldf</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="35" t="str">
@@ -1910,35 +1904,35 @@
 &amp;"EXEC "&amp;$C16&amp;".sys.sp_executesql N'CREATE USER "&amp;$B$5&amp;" FOR LOGIN "&amp;$B$5&amp;"';
 EXEC "&amp;$C16&amp;".sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER "&amp;$B$5&amp;"';"</f>
         <v>INSERT INTO #FileList (LogicalName, PhysicalName, Type, FileGroupName, Size, MaxSize, FileId, CreateLSN, DropLSN, UniqueId, ReadOnlyLSN, ReadWriteLSN, BackupSizeInBytes, SourceBlockSize, FileGroupId, LogGroupGUID, DifferentialBaseLSN, DifferentialBaseGUID, IsReadOnly, IsPresent, TDEThumbprint, SnapshotUrl)
-EXEC ('RESTORE FILELISTONLY FROM DISK = ''E:\BACKUP\AXE_CORE_CLOUD.bak''');
-UPDATE #FileList SET PhysicalPath = 'E:\BACKUP\AXE_CORE_CLOUD.bak' WHERE PhysicalPath IS NULL;
-set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_CLOUD.bak');
-set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_CLOUD.bak');
-RESTORE DATABASE AXE_CORE_CLOUD FROM DISK = 'E:\BACKUP\AXE_CORE_CLOUD.bak'
+EXEC ('RESTORE FILELISTONLY FROM DISK = ''E:\BACKUP\AXE_CORE_2026_CLOUD.bak''');
+UPDATE #FileList SET PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_CLOUD.bak' WHERE PhysicalPath IS NULL;
+set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_CLOUD.bak');
+set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_CLOUD.bak');
+RESTORE DATABASE AXE_CORE_2026_CLOUD FROM DISK = 'E:\BACKUP\AXE_CORE_2026_CLOUD.bak'
 WITH 
-MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_CLOUD.mdf',
-MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_CLOUD.ldf', REPLACE;EXEC AXE_CORE_CLOUD.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
-EXEC AXE_CORE_CLOUD.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
+MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CLOUD.mdf',
+MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CLOUD.ldf', REPLACE;EXEC AXE_CORE_2026_CLOUD.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
+EXEC AXE_CORE_2026_CLOUD.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="B17" s="30" t="str">
         <f>B3&amp;A17</f>
-        <v>E:\BACKUP\AXE_CORE_CNF.bak</v>
+        <v>E:\BACKUP\AXE_CORE_2026_CNF.bak</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="D17" s="30" t="str">
         <f t="shared" ref="D17:D20" si="0">$B$4&amp;$C17&amp;".mdf"</f>
-        <v>E:\DATABASE\AXE_CORE_CNF.bak.mdf</v>
+        <v>E:\DATABASE\AXE_CORE_2026_CNF.bak.mdf</v>
       </c>
       <c r="E17" s="30" t="str">
         <f t="shared" ref="E17:E20" si="1">$B$4&amp;$C17&amp;".ldf"</f>
-        <v>E:\DATABASE\AXE_CORE_CNF.bak.ldf</v>
+        <v>E:\DATABASE\AXE_CORE_2026_CNF.bak.ldf</v>
       </c>
       <c r="F17" s="12"/>
       <c r="G17" s="35" t="str">
@@ -1954,117 +1948,117 @@
 &amp;"EXEC "&amp;$C17&amp;".sys.sp_executesql N'CREATE USER "&amp;$B$5&amp;" FOR LOGIN "&amp;$B$5&amp;"';
 EXEC "&amp;$C17&amp;".sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER "&amp;$B$5&amp;"';"</f>
         <v>INSERT INTO #FileList (LogicalName, PhysicalName, Type, FileGroupName, Size, MaxSize, FileId, CreateLSN, DropLSN, UniqueId, ReadOnlyLSN, ReadWriteLSN, BackupSizeInBytes, SourceBlockSize, FileGroupId, LogGroupGUID, DifferentialBaseLSN, DifferentialBaseGUID, IsReadOnly, IsPresent, TDEThumbprint, SnapshotUrl)
-EXEC ('RESTORE FILELISTONLY FROM DISK = ''E:\BACKUP\AXE_CORE_CNF.bak''');
-UPDATE #FileList SET PhysicalPath = 'E:\BACKUP\AXE_CORE_CNF.bak' WHERE PhysicalPath IS NULL;
-set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_CNF.bak');
-set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_CNF.bak');
-RESTORE DATABASE AXE_CORE_CNF.bak FROM DISK = 'E:\BACKUP\AXE_CORE_CNF.bak'
+EXEC ('RESTORE FILELISTONLY FROM DISK = ''E:\BACKUP\AXE_CORE_2026_CNF.bak''');
+UPDATE #FileList SET PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_CNF.bak' WHERE PhysicalPath IS NULL;
+set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_CNF.bak');
+set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_CNF.bak');
+RESTORE DATABASE AXE_CORE_2026_CNF.bak FROM DISK = 'E:\BACKUP\AXE_CORE_2026_CNF.bak'
 WITH 
-MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_CNF.bak.mdf',
-MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_CNF.bak.ldf', REPLACE;EXEC AXE_CORE_CNF.bak.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
-EXEC AXE_CORE_CNF.bak.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
+MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CNF.bak.mdf',
+MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_2026_CNF.bak.ldf', REPLACE;EXEC AXE_CORE_2026_CNF.bak.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
+EXEC AXE_CORE_2026_CNF.bak.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="B18" s="30" t="str">
         <f>B3&amp;A18</f>
-        <v>E:\BACKUP\AXE_CORE_LOG.bak</v>
+        <v>E:\BACKUP\AXE_CORE_2026_LOG.bak</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="D18" s="30" t="str">
         <f t="shared" si="0"/>
-        <v>E:\DATABASE\AXE_CORE_LOG.bak.mdf</v>
+        <v>E:\DATABASE\AXE_CORE_2026_LOG.bak.mdf</v>
       </c>
       <c r="E18" s="30" t="str">
         <f t="shared" si="1"/>
-        <v>E:\DATABASE\AXE_CORE_LOG.bak.ldf</v>
+        <v>E:\DATABASE\AXE_CORE_2026_LOG.bak.ldf</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="35" t="str">
         <f t="shared" si="2"/>
         <v>INSERT INTO #FileList (LogicalName, PhysicalName, Type, FileGroupName, Size, MaxSize, FileId, CreateLSN, DropLSN, UniqueId, ReadOnlyLSN, ReadWriteLSN, BackupSizeInBytes, SourceBlockSize, FileGroupId, LogGroupGUID, DifferentialBaseLSN, DifferentialBaseGUID, IsReadOnly, IsPresent, TDEThumbprint, SnapshotUrl)
-EXEC ('RESTORE FILELISTONLY FROM DISK = ''E:\BACKUP\AXE_CORE_LOG.bak''');
-UPDATE #FileList SET PhysicalPath = 'E:\BACKUP\AXE_CORE_LOG.bak' WHERE PhysicalPath IS NULL;
-set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_LOG.bak');
-set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_LOG.bak');
-RESTORE DATABASE AXE_CORE_LOG.bak FROM DISK = 'E:\BACKUP\AXE_CORE_LOG.bak'
+EXEC ('RESTORE FILELISTONLY FROM DISK = ''E:\BACKUP\AXE_CORE_2026_LOG.bak''');
+UPDATE #FileList SET PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_LOG.bak' WHERE PhysicalPath IS NULL;
+set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_LOG.bak');
+set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_LOG.bak');
+RESTORE DATABASE AXE_CORE_2026_LOG.bak FROM DISK = 'E:\BACKUP\AXE_CORE_2026_LOG.bak'
 WITH 
-MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_LOG.bak.mdf',
-MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_LOG.bak.ldf', REPLACE;EXEC AXE_CORE_LOG.bak.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
-EXEC AXE_CORE_LOG.bak.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
+MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_2026_LOG.bak.mdf',
+MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_2026_LOG.bak.ldf', REPLACE;EXEC AXE_CORE_2026_LOG.bak.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
+EXEC AXE_CORE_2026_LOG.bak.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="B19" s="30" t="str">
         <f>B3&amp;A19</f>
-        <v>E:\BACKUP\AXE_CORE_MSG.bak</v>
+        <v>E:\BACKUP\AXE_CORE_2026_MSG.bak</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="D19" s="30" t="str">
         <f t="shared" si="0"/>
-        <v>E:\DATABASE\AXE_CORE_MSG.bak.mdf</v>
+        <v>E:\DATABASE\AXE_CORE_2026_MSG.bak.mdf</v>
       </c>
       <c r="E19" s="30" t="str">
         <f t="shared" si="1"/>
-        <v>E:\DATABASE\AXE_CORE_MSG.bak.ldf</v>
+        <v>E:\DATABASE\AXE_CORE_2026_MSG.bak.ldf</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="35" t="str">
         <f t="shared" si="2"/>
         <v>INSERT INTO #FileList (LogicalName, PhysicalName, Type, FileGroupName, Size, MaxSize, FileId, CreateLSN, DropLSN, UniqueId, ReadOnlyLSN, ReadWriteLSN, BackupSizeInBytes, SourceBlockSize, FileGroupId, LogGroupGUID, DifferentialBaseLSN, DifferentialBaseGUID, IsReadOnly, IsPresent, TDEThumbprint, SnapshotUrl)
-EXEC ('RESTORE FILELISTONLY FROM DISK = ''E:\BACKUP\AXE_CORE_MSG.bak''');
-UPDATE #FileList SET PhysicalPath = 'E:\BACKUP\AXE_CORE_MSG.bak' WHERE PhysicalPath IS NULL;
-set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_MSG.bak');
-set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_MSG.bak');
-RESTORE DATABASE AXE_CORE_MSG.bak FROM DISK = 'E:\BACKUP\AXE_CORE_MSG.bak'
+EXEC ('RESTORE FILELISTONLY FROM DISK = ''E:\BACKUP\AXE_CORE_2026_MSG.bak''');
+UPDATE #FileList SET PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_MSG.bak' WHERE PhysicalPath IS NULL;
+set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_MSG.bak');
+set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_MSG.bak');
+RESTORE DATABASE AXE_CORE_2026_MSG.bak FROM DISK = 'E:\BACKUP\AXE_CORE_2026_MSG.bak'
 WITH 
-MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_MSG.bak.mdf',
-MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_MSG.bak.ldf', REPLACE;EXEC AXE_CORE_MSG.bak.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
-EXEC AXE_CORE_MSG.bak.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
+MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_2026_MSG.bak.mdf',
+MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_2026_MSG.bak.ldf', REPLACE;EXEC AXE_CORE_2026_MSG.bak.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
+EXEC AXE_CORE_2026_MSG.bak.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="B20" s="30" t="str">
         <f>B3&amp;A20</f>
-        <v>E:\BACKUP\AXE_CORE_STG.bak</v>
+        <v>E:\BACKUP\AXE_CORE_2026_STG.bak</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="D20" s="30" t="str">
         <f t="shared" si="0"/>
-        <v>E:\DATABASE\AXE_CORE_STG.bak.mdf</v>
+        <v>E:\DATABASE\AXE_CORE_2026_STG.bak.mdf</v>
       </c>
       <c r="E20" s="30" t="str">
         <f t="shared" si="1"/>
-        <v>E:\DATABASE\AXE_CORE_STG.bak.ldf</v>
+        <v>E:\DATABASE\AXE_CORE_2026_STG.bak.ldf</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="35" t="str">
         <f t="shared" si="2"/>
         <v>INSERT INTO #FileList (LogicalName, PhysicalName, Type, FileGroupName, Size, MaxSize, FileId, CreateLSN, DropLSN, UniqueId, ReadOnlyLSN, ReadWriteLSN, BackupSizeInBytes, SourceBlockSize, FileGroupId, LogGroupGUID, DifferentialBaseLSN, DifferentialBaseGUID, IsReadOnly, IsPresent, TDEThumbprint, SnapshotUrl)
-EXEC ('RESTORE FILELISTONLY FROM DISK = ''E:\BACKUP\AXE_CORE_STG.bak''');
-UPDATE #FileList SET PhysicalPath = 'E:\BACKUP\AXE_CORE_STG.bak' WHERE PhysicalPath IS NULL;
-set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_STG.bak');
-set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_STG.bak');
-RESTORE DATABASE AXE_CORE_STG.bak FROM DISK = 'E:\BACKUP\AXE_CORE_STG.bak'
+EXEC ('RESTORE FILELISTONLY FROM DISK = ''E:\BACKUP\AXE_CORE_2026_STG.bak''');
+UPDATE #FileList SET PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_STG.bak' WHERE PhysicalPath IS NULL;
+set @DataLogicalName = (select LogicalName FROM #FileList WHERE Type = 'D' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_STG.bak');
+set @LogLogicalName = (select LogicalName FROM #FileList WHERE Type = 'L' AND PhysicalPath = 'E:\BACKUP\AXE_CORE_2026_STG.bak');
+RESTORE DATABASE AXE_CORE_2026_STG.bak FROM DISK = 'E:\BACKUP\AXE_CORE_2026_STG.bak'
 WITH 
-MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_STG.bak.mdf',
-MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_STG.bak.ldf', REPLACE;EXEC AXE_CORE_STG.bak.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
-EXEC AXE_CORE_STG.bak.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
+MOVE @DataLogicalName TO 'E:\DATABASE\AXE_CORE_2026_STG.bak.mdf',
+MOVE @LogLogicalName TO 'E:\DATABASE\AXE_CORE_2026_STG.bak.ldf', REPLACE;EXEC AXE_CORE_2026_STG.bak.sys.sp_executesql N'CREATE USER dev FOR LOGIN dev';
+EXEC AXE_CORE_2026_STG.bak.sys.sp_executesql N'ALTER ROLE db_owner ADD MEMBER dev';</v>
       </c>
     </row>
   </sheetData>
@@ -2099,9 +2093,9 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="69.21875" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="97.88671875" customWidth="1"/>
+    <col min="4" max="4" width="103.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -2117,43 +2111,45 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="C2" s="9"/>
-      <c r="D2" t="s">
-        <v>70</v>
+      <c r="D2" t="str">
+        <f>"sc create "&amp;B2&amp;" binPath= """&amp;B3&amp;""" start=auto"</f>
+        <v>sc create AXEServiceOCR_CuongTest binPath= "E:\TestTool_Dựng web\ServiceExport\DocProService.exe" start=auto</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="C3" s="9"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="C4" s="9"/>
-      <c r="D4" t="s">
-        <v>75</v>
+      <c r="D4" t="str">
+        <f>"sc create "&amp;B4&amp;" binPath= """&amp;B5&amp;""" start=auto"</f>
+        <v>sc create AXEServiceExport_CuongTest binPath= "E:\TestTool_Dựng web\ServiceOCR\DocProService.exe" start=auto</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="C5" s="9"/>
     </row>
@@ -2197,7 +2193,7 @@
       <c r="C2" s="54"/>
       <c r="G2" s="4"/>
       <c r="H2" s="3" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -2215,7 +2211,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>17</v>
@@ -2231,7 +2227,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>17</v>
@@ -2247,7 +2243,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>17</v>
@@ -2263,7 +2259,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>17</v>
@@ -2279,7 +2275,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>17</v>
@@ -2295,7 +2291,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>17</v>
@@ -2311,7 +2307,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>17</v>
@@ -2327,7 +2323,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>17</v>
@@ -2343,7 +2339,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>17</v>
@@ -2359,7 +2355,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>17</v>
@@ -2419,10 +2415,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>25</v>
@@ -2432,7 +2428,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="2" t="str">
@@ -2442,10 +2438,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>25</v>
@@ -2455,7 +2451,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="2" t="str">
@@ -2465,10 +2461,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>25</v>
@@ -2478,7 +2474,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="2" t="str">
@@ -2488,10 +2484,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>25</v>
@@ -2501,7 +2497,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="2" t="str">
@@ -2511,10 +2507,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>25</v>
@@ -2524,7 +2520,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="2" t="str">
@@ -2534,10 +2530,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>25</v>
@@ -2547,7 +2543,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="2" t="str">
@@ -2557,10 +2553,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>25</v>
@@ -2570,7 +2566,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="2" t="str">
@@ -2580,10 +2576,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>25</v>
@@ -2593,7 +2589,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="2" t="str">
@@ -2603,10 +2599,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>25</v>
@@ -2616,7 +2612,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="2" t="str">
@@ -2626,10 +2622,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>25</v>
@@ -2639,7 +2635,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="2" t="str">
@@ -2659,7 +2655,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="54" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="B28" s="54"/>
       <c r="C28" s="54"/>
@@ -2677,11 +2673,11 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="H30" s="2" t="str">
         <f>IF(C30="","","c:\Windows\system32\inetsrv\appcmd set app "&amp;A30&amp;"/  /"&amp;"applicationPool:"&amp;C30&amp;"")</f>
@@ -2690,11 +2686,11 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H31" s="2" t="str">
         <f t="shared" ref="H31:H39" si="2">IF(C31="","","c:\Windows\system32\inetsrv\appcmd set app "&amp;A31&amp;"/  /"&amp;"applicationPool:"&amp;C31&amp;"")</f>
@@ -2703,11 +2699,11 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="H32" s="2" t="str">
         <f t="shared" si="2"/>
@@ -2716,11 +2712,11 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="H33" s="2" t="str">
         <f t="shared" si="2"/>
@@ -2729,11 +2725,11 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="2" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="H34" s="2" t="str">
         <f t="shared" si="2"/>
@@ -2742,11 +2738,11 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="H35" s="2" t="str">
         <f t="shared" si="2"/>
@@ -2755,11 +2751,11 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="H36" s="2" t="str">
         <f t="shared" si="2"/>
@@ -2768,11 +2764,11 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="H37" s="2" t="str">
         <f t="shared" si="2"/>
@@ -2781,11 +2777,11 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="H38" s="2" t="str">
         <f t="shared" si="2"/>
@@ -2794,11 +2790,11 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="H39" s="2" t="str">
         <f t="shared" si="2"/>
@@ -2831,6 +2827,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Ghich_x00fa_ xmlns="97d068c0-5bfb-413b-9996-819e39fdf128" xsi:nil="true"/>
+    <TaxCatchAll xmlns="2c7f0914-2907-4374-a90b-da4fc7d9e6d0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="97d068c0-5bfb-413b-9996-819e39fdf128">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010097FE9C0C8E574444875F1CBBF8414DDA" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c7e0992f45b677c2156c5ab52d17057f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="97d068c0-5bfb-413b-9996-819e39fdf128" xmlns:ns3="2c7f0914-2907-4374-a90b-da4fc7d9e6d0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2f06a3ea3329379ac3c4a4f5da7fed49" ns2:_="" ns3:_="">
     <xsd:import namespace="97d068c0-5bfb-413b-9996-819e39fdf128"/>
@@ -3065,28 +3082,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Ghich_x00fa_ xmlns="97d068c0-5bfb-413b-9996-819e39fdf128" xsi:nil="true"/>
-    <TaxCatchAll xmlns="2c7f0914-2907-4374-a90b-da4fc7d9e6d0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="97d068c0-5bfb-413b-9996-819e39fdf128">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FDEE16B-9D1D-4FD0-B127-E14D995BDF2D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA8505A6-C0ED-439D-B023-AA9B1B1662BB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="97d068c0-5bfb-413b-9996-819e39fdf128"/>
+    <ds:schemaRef ds:uri="2c7f0914-2907-4374-a90b-da4fc7d9e6d0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E3A15DF-6B1B-40AC-992D-CB264AF46DCF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3103,23 +3118,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA8505A6-C0ED-439D-B023-AA9B1B1662BB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="97d068c0-5bfb-413b-9996-819e39fdf128"/>
-    <ds:schemaRef ds:uri="2c7f0914-2907-4374-a90b-da4fc7d9e6d0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FDEE16B-9D1D-4FD0-B127-E14D995BDF2D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>